--- a/output/2026-10-02_03_Malesia_Melaka_ATEX_Equipment_Services.xlsx
+++ b/output/2026-10-02_03_Malesia_Melaka_ATEX_Equipment_Services.xlsx
@@ -550,7 +550,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Verificato via WebFetch sito ufficiale: sezione dedicata 'Explosion Proof' presente nel catalogo prodotti.</t>
+          <t>Verificato via WebFetch sito ufficiale: sezione dedicata 'Explosion Proof' presente nel catalogo prodotti. [DUPLICATO — vedi anche: 2026-10-01_03_Malesia_Kedah_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Verificato via WebFetch (catalogo EExd/EExde junction box e proiettori Stahl/Cortem) + WebSearch (businesslist.my) che conferma indirizzo Puchong Selangor, telefono ed email.</t>
+          <t>Verificato via WebFetch (catalogo EExd/EExde junction box e proiettori Stahl/Cortem) + WebSearch (businesslist.my) che conferma indirizzo Puchong Selangor, telefono ed email. [DUPLICATO — vedi anche: 2026-10-01_03_Malesia_Kedah_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Verificato via WebSearch (sito con errore 503 al fetch diretto, ma snippet e pagine prodotto confermano ventilatori ATEX e lampade SUPAKU explosion-proof ATEX); indirizzo No.1 Jalan BK5b/3, Bandar Kinrara, 47180 Puchong, Selangor.</t>
+          <t>Verificato via WebSearch (sito con errore 503 al fetch diretto, ma snippet e pagine prodotto confermano ventilatori ATEX e lampade SUPAKU explosion-proof ATEX); indirizzo No.1 Jalan BK5b/3, Bandar Kinrara, 47180 Puchong, Selangor. [DUPLICATO — vedi anche: 2026-10-01_03_Malesia_Kedah_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
